--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_CARLA_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_CARLA_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DB094F-74D0-4B7C-955D-9E9AC5039E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0A5FE6-98D9-40CF-A426-FC892141DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -621,21 +621,6 @@
     <t>f1_htn_kora;f2_htn_kora;f1_untdat;f2_untdat;gebdat</t>
   </si>
   <si>
-    <t>case_when(
-      f1_htn_kora == 1 | f2_htn_kora == 1 ~ 1,
-      f1_htn_kora == 0 &amp; f2_htn_kora == 0 ~ 0,
-      TRUE ~ NA_integer_
-    )</t>
-  </si>
-  <si>
-    <t>case_when(                                                                                                                                                                                                                                                                                                                                                                                                                                
-  hyp_i == 1 ~ 1, 
-  hyp_i == 2 ~ 0, 
-  is.na(hyp_i) &amp; htn_kora == 1 ~ 1,
-  is.na(hyp_i) &amp; htn_kora == 0 ~ 0, 
-  TRUE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>ifelse(is.na(cignr_day),
                       ifelse(is.na(cigarnr_day), 
                              ifelse(is.na(pipe_day),0,pipe_day*5),
@@ -679,10 +664,27 @@
     <t>gebdat;f1_untdat;f2_untdat</t>
   </si>
   <si>
-    <t>as.numeric(f2_insuff_date-gebdat)/365.25</t>
-  </si>
-  <si>
     <t>as.numeric(tod_dat-gebdat)/365.25</t>
+  </si>
+  <si>
+    <t>case_when(                                                                                                                                                                                                                                                                                                                                                                                                                                
+  hyp_i == 1 | htn_kora == 1 ~ 1, 
+  hyp_i == 2 &amp; htn_kora == 0 ~ 0, 
+  is.na(hyp_i) &amp; htn_kora == 0 ~ 0,
+  is.na(htn_kora) &amp; hyp_i == 2 ~ 0, 
+  TRUE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>case_when(
+  f1_htn_kora == 1 | f2_htn_kora == 1 ~ 1,
+  f1_htn_kora == 0 &amp; f2_htn_kora == 0 ~ 0,
+  is.na(f1_htn_kora) &amp; f2_htn_kora == 0 ~ 0,
+  is.na(f2_htn_kora) &amp; f1_htn_kora == 0 ~ 0,
+  TRUE ~ NA_integer_
+)</t>
+  </si>
+  <si>
+    <t>as.numeric(as.Date(f2_insuff_date)-as.Date(gebdat))/365.25</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1444,7 @@
         <v>142</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="4" t="s">
@@ -1521,10 +1523,10 @@
         <v>139</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>134</v>
@@ -1674,7 +1676,7 @@
         <v>139</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>147</v>
@@ -1752,10 +1754,10 @@
         <v>145</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>147</v>
@@ -1781,10 +1783,10 @@
         <v>145</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>147</v>
@@ -1810,10 +1812,10 @@
         <v>145</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>147</v>
@@ -2321,7 +2323,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="2:11" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:11" s="12" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>105</v>
       </c>
@@ -2338,7 +2340,7 @@
         <v>139</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>182</v>
@@ -2367,7 +2369,7 @@
         <v>139</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>183</v>
@@ -2425,7 +2427,7 @@
         <v>142</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I51" s="16" t="s">
         <v>162</v>
@@ -2603,7 +2605,7 @@
         <v>142</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I58" s="14" t="s">
         <v>181</v>
@@ -2674,13 +2676,13 @@
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G61" s="12" t="s">
         <v>142</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="12" t="s">
